--- a/data/processed/website_clean.xlsx
+++ b/data/processed/website_clean.xlsx
@@ -19606,12 +19606,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Daveâ€™s Bakery, Sitio Tablogon,City of Escalante,6124</t>
+          <t>Dave’s Bakery, Sitio Tablogon,City of Escalante,6124</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Daveâ€™s Bakery, Sitio Tablogon,City of Escalante,6124</t>
+          <t>Dave’s Bakery, Sitio Tablogon,City of Escalante,6124</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -67222,12 +67222,12 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Governor Forbes Skyloft Hotel And Residences, 1160, Barangay 478, Unit â€”â€”,City of Manila,1160</t>
+          <t>Governor Forbes Skyloft Hotel And Residences, 1160, Barangay 478, Unit ——,City of Manila,1160</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Governor Forbes Skyloft Hotel And Residences, 1160, Barangay 478, Unit â€”â€”,City of Manila,1160</t>
+          <t>Governor Forbes Skyloft Hotel And Residences, 1160, Barangay 478, Unit ——,City of Manila,1160</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
